--- a/tests/fixtures/inventarios/inventario_complementario_pruebas.xlsx
+++ b/tests/fixtures/inventarios/inventario_complementario_pruebas.xlsx
@@ -4,7 +4,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Inventario" sheetId="1" r:id="rId1"/>
+    <sheet name="Casos de prueba" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Inventario!$A$1:$N$33</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -397,19 +401,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:N33"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,730 +433,1860 @@
         <v>MODELO</v>
       </c>
       <c r="E1" t="str">
+        <v>SERIE</v>
+      </c>
+      <c r="F1" t="str">
         <v>PROVEEDOR</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>OBSERVACIONES</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>CÓDIGO INTERNO</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>ID</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>CÓDIGO DE BARRAS</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>QR</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>PLACA LOCAL</v>
+      </c>
+      <c r="M1" t="str">
+        <v>ETIQUETADO</v>
+      </c>
+      <c r="N1" t="str">
+        <v>CANTIDAD ACTUAL</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Material QA Probeta graduada 1</v>
+        <v>Flexómetro</v>
       </c>
       <c r="B2" t="str">
-        <v>51 unidad</v>
+        <v>20 unidades</v>
       </c>
       <c r="C2" t="str">
-        <v>Marca QA Centro</v>
+        <v>Genérica</v>
       </c>
       <c r="D2" t="str">
-        <v>MODELO-QA-001-5299</v>
+        <v>5 m</v>
       </c>
       <c r="E2" t="str">
-        <v>Proveedor ficticio QA-2</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>CODIGO-QA-001-1451</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>ID-QA-001-6603</v>
+        <v>INT-MAT-001</v>
       </c>
       <c r="I2" t="str">
-        <v>BARRAS-QA-001-2116</v>
+        <v>ID-MAT-001</v>
       </c>
       <c r="J2" t="str">
-        <v>QR-QA-001-9861</v>
+        <v>BAR-MAT-001</v>
       </c>
       <c r="K2" t="str">
-        <v>LOCAL-QA-001-2621</v>
+        <v>QR-MAT-001</v>
+      </c>
+      <c r="L2" t="str">
+        <v>LOC-MAT-001</v>
+      </c>
+      <c r="M2" t="str">
+        <v>TAG-MAT-001</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Material QA Probeta graduada 2</v>
+        <v>Soporte universal</v>
       </c>
       <c r="B3" t="str">
-        <v>79 unidad</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v>MODELO-QA-002-2158</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>CODIGO-QA-002-9385</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>ID-QA-002-1246</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>BARRAS-QA-002-2933</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>QR-QA-002-2078</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>LOCAL-QA-002-3835</v>
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Material QA Espátula de laboratorio 3</v>
+        <v>Manguera de silicona</v>
       </c>
       <c r="B4" t="str">
-        <v>98 unidad</v>
+        <v>2,5 m</v>
       </c>
       <c r="C4" t="str">
-        <v>Marca de prueba Uno</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>MODELO-QA-003-6781</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>Proveedor ficticio QA-2</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>CODIGO-QA-003-4797</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>ID-QA-003-5228</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>BARRAS-QA-003-6601</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v>QR-QA-003-6947</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v>LOCAL-QA-003-7700</v>
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Material QA Frasco lavador 4</v>
+        <v/>
       </c>
       <c r="B5" t="str">
-        <v>33 unidad</v>
+        <v>4 unidades</v>
       </c>
       <c r="C5" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>MODELO-QA-004-7981</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>CODIGO-QA-004-6756</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>ID-QA-004-3110</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>BARRAS-QA-004-3621</v>
+        <v/>
       </c>
       <c r="J5" t="str">
-        <v>QR-QA-004-6697</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>LOCAL-QA-004-4916</v>
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Material QA Guantes de protección 5</v>
+        <v>Material con cantidad negativa</v>
       </c>
       <c r="B6" t="str">
-        <v>95 unidad</v>
+        <v>-3 kg</v>
       </c>
       <c r="C6" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>MODELO-QA-005-4471</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>CODIGO-QA-005-2749</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>ID-QA-005-5471</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>BARRAS-QA-005-7503</v>
+        <v/>
       </c>
       <c r="J6" t="str">
-        <v>QR-QA-005-9150</v>
+        <v/>
       </c>
       <c r="K6" t="str">
-        <v>LOCAL-QA-005-5792</v>
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Material QA Papel indicador 6</v>
+        <v>Material con cantidad textual</v>
       </c>
       <c r="B7" t="str">
-        <v>49 unidad</v>
+        <v>tres unidades</v>
       </c>
       <c r="C7" t="str">
-        <v>Marca QA Sur</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>MODELO-QA-006-1017</v>
+        <v/>
       </c>
       <c r="E7" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>CODIGO-QA-006-3385</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>ID-QA-006-3763</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>BARRAS-QA-006-7274</v>
+        <v/>
       </c>
       <c r="J7" t="str">
-        <v>QR-QA-006-8581</v>
+        <v/>
       </c>
       <c r="K7" t="str">
-        <v>LOCAL-QA-006-8810</v>
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Material QA Soporte para tubos 7</v>
+        <v>Material con precisión excesiva</v>
       </c>
       <c r="B8" t="str">
-        <v>57 unidad</v>
+        <v>1.2345 kg</v>
       </c>
       <c r="C8" t="str">
-        <v>Marca de prueba Uno</v>
+        <v/>
       </c>
       <c r="D8" t="str">
-        <v>MODELO-QA-007-4294</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>Proveedor ficticio QA-2</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>CODIGO-QA-007-9021</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>ID-QA-007-7564</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>BARRAS-QA-007-5826</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>QR-QA-007-8740</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>LOCAL-QA-007-2439</v>
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Material QA Pinza universal 8</v>
+        <v>Material con cantidad fuera de rango</v>
       </c>
       <c r="B9" t="str">
-        <v>25 unidad</v>
+        <v>100000000000 kg</v>
       </c>
       <c r="C9" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>MODELO-QA-008-8014</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>CODIGO-QA-008-5260</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>ID-QA-008-3428</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>BARRAS-QA-008-5006</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>QR-QA-008-7889</v>
+        <v/>
       </c>
       <c r="K9" t="str">
-        <v>LOCAL-QA-008-3241</v>
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Material QA Gradilla plástica 9</v>
+        <v>Material con QR repetido</v>
       </c>
       <c r="B10" t="str">
-        <v>66 unidad</v>
+        <v/>
       </c>
       <c r="C10" t="str">
-        <v>Marca QA Sur</v>
+        <v/>
       </c>
       <c r="D10" t="str">
-        <v>MODELO-QA-009-9173</v>
+        <v/>
       </c>
       <c r="E10" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>CODIGO-QA-009-4983</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>ID-QA-009-9404</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>BARRAS-QA-009-6973</v>
+        <v/>
       </c>
       <c r="J10" t="str">
-        <v>QR-QA-009-2380</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v>LOCAL-QA-009-8067</v>
+        <v>QR-MAT-001</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Material QA Probeta graduada 10</v>
+        <v>Material con código interno repetido</v>
       </c>
       <c r="B11" t="str">
-        <v>56 unidad</v>
+        <v/>
       </c>
       <c r="C11" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="D11" t="str">
-        <v>MODELO-QA-010-8151</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>CODIGO-QA-010-4429</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>ID-QA-010-2906</v>
+        <v>INT-MAT-001</v>
       </c>
       <c r="I11" t="str">
-        <v>BARRAS-QA-010-4997</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>QR-QA-010-2559</v>
+        <v/>
       </c>
       <c r="K11" t="str">
-        <v>LOCAL-QA-010-1039</v>
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Material QA Puntas para pipeta 11</v>
+        <v>Material con observación extensa</v>
       </c>
       <c r="B12" t="str">
-        <v>1 unidad</v>
+        <v/>
       </c>
       <c r="C12" t="str">
-        <v>Marca de prueba Uno</v>
+        <v/>
       </c>
       <c r="D12" t="str">
-        <v>MODELO-QA-011-1065</v>
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>CODIGO-QA-011-6697</v>
+        <v>OOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOOO</v>
       </c>
       <c r="H12" t="str">
-        <v>ID-QA-011-7312</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>BARRAS-QA-011-7184</v>
+        <v/>
       </c>
       <c r="J12" t="str">
-        <v>QR-QA-011-3266</v>
+        <v/>
       </c>
       <c r="K12" t="str">
-        <v>LOCAL-QA-011-1040</v>
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Material QA Soporte para tubos 12</v>
+        <v>DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD</v>
       </c>
       <c r="B13" t="str">
-        <v>63 unidad</v>
+        <v/>
       </c>
       <c r="C13" t="str">
-        <v>Marca QA Centro</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>MODELO-QA-012-1257</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>CODIGO-QA-012-9516</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>ID-QA-012-8297</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>BARRAS-QA-012-3834</v>
+        <v/>
       </c>
       <c r="J13" t="str">
-        <v>QR-QA-012-5740</v>
+        <v/>
       </c>
       <c r="K13" t="str">
-        <v>LOCAL-QA-012-7390</v>
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Material QA Espátula de laboratorio 13</v>
+        <v>Material con modelo extenso</v>
       </c>
       <c r="B14" t="str">
-        <v>32 unidad</v>
+        <v/>
       </c>
       <c r="C14" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>MODELO-QA-013-5754</v>
+        <v>MMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMMM</v>
       </c>
       <c r="E14" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>CODIGO-QA-013-8965</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>ID-QA-013-7996</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>BARRAS-QA-013-8776</v>
+        <v/>
       </c>
       <c r="J14" t="str">
-        <v>QR-QA-013-5597</v>
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v>LOCAL-QA-013-4435</v>
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Material QA Pinza universal 14</v>
+        <v>Material con cantidades contradictorias</v>
       </c>
       <c r="B15" t="str">
-        <v>39 unidad</v>
+        <v>2 unidades</v>
       </c>
       <c r="C15" t="str">
-        <v>Marca de prueba Uno</v>
+        <v/>
       </c>
       <c r="D15" t="str">
-        <v>MODELO-QA-014-9912</v>
+        <v/>
       </c>
       <c r="E15" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>CODIGO-QA-014-2957</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>ID-QA-014-9241</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>BARRAS-QA-014-5688</v>
+        <v/>
       </c>
       <c r="J15" t="str">
-        <v>QR-QA-014-2894</v>
+        <v/>
       </c>
       <c r="K15" t="str">
-        <v>LOCAL-QA-014-2450</v>
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v>3 unidades</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Material QA Probeta graduada 15</v>
+        <v>Material con unidad extensa</v>
       </c>
       <c r="B16" t="str">
-        <v>32 unidad</v>
+        <v>1 ggggggggggggggggggggggggggggggggggggggggggggggggggg</v>
       </c>
       <c r="C16" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="D16" t="str">
-        <v>MODELO-QA-015-9313</v>
+        <v/>
       </c>
       <c r="E16" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>CODIGO-QA-015-2195</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>ID-QA-015-7244</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>BARRAS-QA-015-7628</v>
+        <v/>
       </c>
       <c r="J16" t="str">
-        <v>QR-QA-015-6148</v>
+        <v/>
       </c>
       <c r="K16" t="str">
-        <v>LOCAL-QA-015-7760</v>
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Material QA Guantes de protección 16</v>
+        <v>Material con identificador extenso</v>
       </c>
       <c r="B17" t="str">
-        <v>63 unidad</v>
+        <v/>
       </c>
       <c r="C17" t="str">
-        <v>Marca QA Norte</v>
+        <v/>
       </c>
       <c r="D17" t="str">
-        <v>MODELO-QA-016-3749</v>
+        <v/>
       </c>
       <c r="E17" t="str">
-        <v>Proveedor ficticio QA-2</v>
+        <v/>
       </c>
       <c r="F17" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>CODIGO-QA-016-6710</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>ID-QA-016-1809</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>BARRAS-QA-016-2071</v>
+        <v>IIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIIII</v>
       </c>
       <c r="J17" t="str">
-        <v>QR-QA-016-5456</v>
+        <v/>
       </c>
       <c r="K17" t="str">
-        <v>LOCAL-QA-016-1979</v>
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Material QA Pinza universal 17</v>
+        <v>Pinza para tubo</v>
       </c>
       <c r="B18" t="str">
-        <v>98 unidad</v>
+        <v>0 unidades</v>
       </c>
       <c r="C18" t="str">
-        <v>Marca de prueba Uno</v>
+        <v/>
       </c>
       <c r="D18" t="str">
-        <v>MODELO-QA-017-5874</v>
+        <v/>
       </c>
       <c r="E18" t="str">
-        <v>Proveedor de pruebas</v>
+        <v/>
       </c>
       <c r="F18" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>CODIGO-QA-017-1853</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>ID-QA-017-6249</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>BARRAS-QA-017-2398</v>
+        <v/>
       </c>
       <c r="J18" t="str">
-        <v>QR-QA-017-3720</v>
+        <v/>
       </c>
       <c r="K18" t="str">
-        <v>LOCAL-QA-017-4571</v>
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Material QA Probeta graduada 18</v>
+        <v>Consumible de prueba 001</v>
       </c>
       <c r="B19" t="str">
-        <v>85 unidad</v>
+        <v>5 unidades</v>
       </c>
       <c r="C19" t="str">
-        <v>Marca de prueba Uno</v>
+        <v>Marca Demo</v>
       </c>
       <c r="D19" t="str">
-        <v>MODELO-QA-018-1488</v>
+        <v>MOD-MAT-001</v>
       </c>
       <c r="E19" t="str">
-        <v>Proveedor ficticio QA-1</v>
+        <v>SER-MAT-ADIC-001</v>
       </c>
       <c r="F19" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v>Proveedor Genérico</v>
       </c>
       <c r="G19" t="str">
-        <v>CODIGO-QA-018-7381</v>
+        <v>Caso exitoso adicional 001.</v>
       </c>
       <c r="H19" t="str">
-        <v>ID-QA-018-1172</v>
+        <v>INT-MAT-ADIC-001</v>
       </c>
       <c r="I19" t="str">
-        <v>BARRAS-QA-018-7464</v>
+        <v>ID-MAT-ADIC-001</v>
       </c>
       <c r="J19" t="str">
-        <v>QR-QA-018-8803</v>
+        <v>BAR-MAT-ADIC-001</v>
       </c>
       <c r="K19" t="str">
-        <v>LOCAL-QA-018-1889</v>
+        <v>QR-MAT-ADIC-001</v>
+      </c>
+      <c r="L19" t="str">
+        <v>LOC-MAT-ADIC-001</v>
+      </c>
+      <c r="M19" t="str">
+        <v>TAG-MAT-ADIC-001</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Material QA Papel indicador 19</v>
+        <v>Consumible de prueba 002</v>
       </c>
       <c r="B20" t="str">
-        <v>6 unidad</v>
+        <v>2,5 m</v>
       </c>
       <c r="C20" t="str">
-        <v>Marca QA Centro</v>
+        <v>Marca Demo</v>
       </c>
       <c r="D20" t="str">
-        <v>MODELO-QA-019-5737</v>
+        <v>MOD-MAT-002</v>
       </c>
       <c r="E20" t="str">
-        <v>Proveedor de pruebas</v>
+        <v>SER-MAT-ADIC-002</v>
       </c>
       <c r="F20" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v>Proveedor Genérico</v>
       </c>
       <c r="G20" t="str">
-        <v>CODIGO-QA-019-2913</v>
+        <v>Caso exitoso adicional 002.</v>
       </c>
       <c r="H20" t="str">
-        <v>ID-QA-019-8436</v>
+        <v>INT-MAT-ADIC-002</v>
       </c>
       <c r="I20" t="str">
-        <v>BARRAS-QA-019-5912</v>
+        <v>ID-MAT-ADIC-002</v>
       </c>
       <c r="J20" t="str">
-        <v>QR-QA-019-3397</v>
+        <v>BAR-MAT-ADIC-002</v>
       </c>
       <c r="K20" t="str">
-        <v>LOCAL-QA-019-1451</v>
+        <v>QR-MAT-ADIC-002</v>
+      </c>
+      <c r="L20" t="str">
+        <v>LOC-MAT-ADIC-002</v>
+      </c>
+      <c r="M20" t="str">
+        <v>TAG-MAT-ADIC-002</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Material QA Pinza universal 20</v>
+        <v>Consumible de prueba 003</v>
       </c>
       <c r="B21" t="str">
-        <v>64 unidad</v>
+        <v>0 unidades</v>
       </c>
       <c r="C21" t="str">
-        <v>Marca de prueba Uno</v>
+        <v>Marca Demo</v>
       </c>
       <c r="D21" t="str">
-        <v>MODELO-QA-020-1088</v>
+        <v>MOD-MAT-003</v>
       </c>
       <c r="E21" t="str">
-        <v>Proveedor de pruebas</v>
+        <v>SER-MAT-ADIC-003</v>
       </c>
       <c r="F21" t="str">
-        <v>Dato sintético de prueba; no corresponde a inventario real.</v>
+        <v>Proveedor Genérico</v>
       </c>
       <c r="G21" t="str">
-        <v>CODIGO-QA-020-2004</v>
+        <v>Caso exitoso adicional 003.</v>
       </c>
       <c r="H21" t="str">
-        <v>ID-QA-020-5218</v>
+        <v>INT-MAT-ADIC-003</v>
       </c>
       <c r="I21" t="str">
-        <v>BARRAS-QA-020-7707</v>
+        <v>ID-MAT-ADIC-003</v>
       </c>
       <c r="J21" t="str">
-        <v>QR-QA-020-8531</v>
+        <v>BAR-MAT-ADIC-003</v>
       </c>
       <c r="K21" t="str">
-        <v>LOCAL-QA-020-3938</v>
+        <v>QR-MAT-ADIC-003</v>
+      </c>
+      <c r="L21" t="str">
+        <v>LOC-MAT-ADIC-003</v>
+      </c>
+      <c r="M21" t="str">
+        <v>TAG-MAT-ADIC-003</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Consumible de prueba 004</v>
+      </c>
+      <c r="B22" t="str">
+        <v>10 pares</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D22" t="str">
+        <v>MOD-MAT-004</v>
+      </c>
+      <c r="E22" t="str">
+        <v>SER-MAT-ADIC-004</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Caso exitoso adicional 004.</v>
+      </c>
+      <c r="H22" t="str">
+        <v>INT-MAT-ADIC-004</v>
+      </c>
+      <c r="I22" t="str">
+        <v>ID-MAT-ADIC-004</v>
+      </c>
+      <c r="J22" t="str">
+        <v>BAR-MAT-ADIC-004</v>
+      </c>
+      <c r="K22" t="str">
+        <v>QR-MAT-ADIC-004</v>
+      </c>
+      <c r="L22" t="str">
+        <v>LOC-MAT-ADIC-004</v>
+      </c>
+      <c r="M22" t="str">
+        <v>TAG-MAT-ADIC-004</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Consumible de prueba 005</v>
+      </c>
+      <c r="B23" t="str">
+        <v>1.25 kg</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D23" t="str">
+        <v>MOD-MAT-005</v>
+      </c>
+      <c r="E23" t="str">
+        <v>SER-MAT-ADIC-005</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Caso exitoso adicional 005.</v>
+      </c>
+      <c r="H23" t="str">
+        <v>INT-MAT-ADIC-005</v>
+      </c>
+      <c r="I23" t="str">
+        <v>ID-MAT-ADIC-005</v>
+      </c>
+      <c r="J23" t="str">
+        <v>BAR-MAT-ADIC-005</v>
+      </c>
+      <c r="K23" t="str">
+        <v>QR-MAT-ADIC-005</v>
+      </c>
+      <c r="L23" t="str">
+        <v>LOC-MAT-ADIC-005</v>
+      </c>
+      <c r="M23" t="str">
+        <v>TAG-MAT-ADIC-005</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Consumible de prueba 006</v>
+      </c>
+      <c r="B24" t="str">
+        <v>5 unidades</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D24" t="str">
+        <v>MOD-MAT-006</v>
+      </c>
+      <c r="E24" t="str">
+        <v>SER-MAT-ADIC-006</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Caso exitoso adicional 006.</v>
+      </c>
+      <c r="H24" t="str">
+        <v>INT-MAT-ADIC-006</v>
+      </c>
+      <c r="I24" t="str">
+        <v>ID-MAT-ADIC-006</v>
+      </c>
+      <c r="J24" t="str">
+        <v>BAR-MAT-ADIC-006</v>
+      </c>
+      <c r="K24" t="str">
+        <v>QR-MAT-ADIC-006</v>
+      </c>
+      <c r="L24" t="str">
+        <v>LOC-MAT-ADIC-006</v>
+      </c>
+      <c r="M24" t="str">
+        <v>TAG-MAT-ADIC-006</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Consumible de prueba 007</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2,5 m</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D25" t="str">
+        <v>MOD-MAT-007</v>
+      </c>
+      <c r="E25" t="str">
+        <v>SER-MAT-ADIC-007</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Caso exitoso adicional 007.</v>
+      </c>
+      <c r="H25" t="str">
+        <v>INT-MAT-ADIC-007</v>
+      </c>
+      <c r="I25" t="str">
+        <v>ID-MAT-ADIC-007</v>
+      </c>
+      <c r="J25" t="str">
+        <v>BAR-MAT-ADIC-007</v>
+      </c>
+      <c r="K25" t="str">
+        <v>QR-MAT-ADIC-007</v>
+      </c>
+      <c r="L25" t="str">
+        <v>LOC-MAT-ADIC-007</v>
+      </c>
+      <c r="M25" t="str">
+        <v>TAG-MAT-ADIC-007</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Consumible de prueba 008</v>
+      </c>
+      <c r="B26" t="str">
+        <v>0 unidades</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D26" t="str">
+        <v>MOD-MAT-008</v>
+      </c>
+      <c r="E26" t="str">
+        <v>SER-MAT-ADIC-008</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Caso exitoso adicional 008.</v>
+      </c>
+      <c r="H26" t="str">
+        <v>INT-MAT-ADIC-008</v>
+      </c>
+      <c r="I26" t="str">
+        <v>ID-MAT-ADIC-008</v>
+      </c>
+      <c r="J26" t="str">
+        <v>BAR-MAT-ADIC-008</v>
+      </c>
+      <c r="K26" t="str">
+        <v>QR-MAT-ADIC-008</v>
+      </c>
+      <c r="L26" t="str">
+        <v>LOC-MAT-ADIC-008</v>
+      </c>
+      <c r="M26" t="str">
+        <v>TAG-MAT-ADIC-008</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Consumible de prueba 009</v>
+      </c>
+      <c r="B27" t="str">
+        <v>10 pares</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D27" t="str">
+        <v>MOD-MAT-009</v>
+      </c>
+      <c r="E27" t="str">
+        <v>SER-MAT-ADIC-009</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Caso exitoso adicional 009.</v>
+      </c>
+      <c r="H27" t="str">
+        <v>INT-MAT-ADIC-009</v>
+      </c>
+      <c r="I27" t="str">
+        <v>ID-MAT-ADIC-009</v>
+      </c>
+      <c r="J27" t="str">
+        <v>BAR-MAT-ADIC-009</v>
+      </c>
+      <c r="K27" t="str">
+        <v>QR-MAT-ADIC-009</v>
+      </c>
+      <c r="L27" t="str">
+        <v>LOC-MAT-ADIC-009</v>
+      </c>
+      <c r="M27" t="str">
+        <v>TAG-MAT-ADIC-009</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Consumible de prueba 010</v>
+      </c>
+      <c r="B28" t="str">
+        <v>1.25 kg</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D28" t="str">
+        <v>MOD-MAT-010</v>
+      </c>
+      <c r="E28" t="str">
+        <v>SER-MAT-ADIC-010</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Caso exitoso adicional 010.</v>
+      </c>
+      <c r="H28" t="str">
+        <v>INT-MAT-ADIC-010</v>
+      </c>
+      <c r="I28" t="str">
+        <v>ID-MAT-ADIC-010</v>
+      </c>
+      <c r="J28" t="str">
+        <v>BAR-MAT-ADIC-010</v>
+      </c>
+      <c r="K28" t="str">
+        <v>QR-MAT-ADIC-010</v>
+      </c>
+      <c r="L28" t="str">
+        <v>LOC-MAT-ADIC-010</v>
+      </c>
+      <c r="M28" t="str">
+        <v>TAG-MAT-ADIC-010</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Consumible de prueba 011</v>
+      </c>
+      <c r="B29" t="str">
+        <v>5 unidades</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D29" t="str">
+        <v>MOD-MAT-011</v>
+      </c>
+      <c r="E29" t="str">
+        <v>SER-MAT-ADIC-011</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Caso exitoso adicional 011.</v>
+      </c>
+      <c r="H29" t="str">
+        <v>INT-MAT-ADIC-011</v>
+      </c>
+      <c r="I29" t="str">
+        <v>ID-MAT-ADIC-011</v>
+      </c>
+      <c r="J29" t="str">
+        <v>BAR-MAT-ADIC-011</v>
+      </c>
+      <c r="K29" t="str">
+        <v>QR-MAT-ADIC-011</v>
+      </c>
+      <c r="L29" t="str">
+        <v>LOC-MAT-ADIC-011</v>
+      </c>
+      <c r="M29" t="str">
+        <v>TAG-MAT-ADIC-011</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Consumible de prueba 012</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2,5 m</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D30" t="str">
+        <v>MOD-MAT-012</v>
+      </c>
+      <c r="E30" t="str">
+        <v>SER-MAT-ADIC-012</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Caso exitoso adicional 012.</v>
+      </c>
+      <c r="H30" t="str">
+        <v>INT-MAT-ADIC-012</v>
+      </c>
+      <c r="I30" t="str">
+        <v>ID-MAT-ADIC-012</v>
+      </c>
+      <c r="J30" t="str">
+        <v>BAR-MAT-ADIC-012</v>
+      </c>
+      <c r="K30" t="str">
+        <v>QR-MAT-ADIC-012</v>
+      </c>
+      <c r="L30" t="str">
+        <v>LOC-MAT-ADIC-012</v>
+      </c>
+      <c r="M30" t="str">
+        <v>TAG-MAT-ADIC-012</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Consumible de prueba 013</v>
+      </c>
+      <c r="B31" t="str">
+        <v>0 unidades</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D31" t="str">
+        <v>MOD-MAT-013</v>
+      </c>
+      <c r="E31" t="str">
+        <v>SER-MAT-ADIC-013</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Caso exitoso adicional 013.</v>
+      </c>
+      <c r="H31" t="str">
+        <v>INT-MAT-ADIC-013</v>
+      </c>
+      <c r="I31" t="str">
+        <v>ID-MAT-ADIC-013</v>
+      </c>
+      <c r="J31" t="str">
+        <v>BAR-MAT-ADIC-013</v>
+      </c>
+      <c r="K31" t="str">
+        <v>QR-MAT-ADIC-013</v>
+      </c>
+      <c r="L31" t="str">
+        <v>LOC-MAT-ADIC-013</v>
+      </c>
+      <c r="M31" t="str">
+        <v>TAG-MAT-ADIC-013</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Consumible de prueba 014</v>
+      </c>
+      <c r="B32" t="str">
+        <v>10 pares</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D32" t="str">
+        <v>MOD-MAT-014</v>
+      </c>
+      <c r="E32" t="str">
+        <v>SER-MAT-ADIC-014</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Caso exitoso adicional 014.</v>
+      </c>
+      <c r="H32" t="str">
+        <v>INT-MAT-ADIC-014</v>
+      </c>
+      <c r="I32" t="str">
+        <v>ID-MAT-ADIC-014</v>
+      </c>
+      <c r="J32" t="str">
+        <v>BAR-MAT-ADIC-014</v>
+      </c>
+      <c r="K32" t="str">
+        <v>QR-MAT-ADIC-014</v>
+      </c>
+      <c r="L32" t="str">
+        <v>LOC-MAT-ADIC-014</v>
+      </c>
+      <c r="M32" t="str">
+        <v>TAG-MAT-ADIC-014</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Consumible de prueba 015</v>
+      </c>
+      <c r="B33" t="str">
+        <v>1.25 kg</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Marca Demo</v>
+      </c>
+      <c r="D33" t="str">
+        <v>MOD-MAT-015</v>
+      </c>
+      <c r="E33" t="str">
+        <v>SER-MAT-ADIC-015</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Proveedor Genérico</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Caso exitoso adicional 015.</v>
+      </c>
+      <c r="H33" t="str">
+        <v>INT-MAT-ADIC-015</v>
+      </c>
+      <c r="I33" t="str">
+        <v>ID-MAT-ADIC-015</v>
+      </c>
+      <c r="J33" t="str">
+        <v>BAR-MAT-ADIC-015</v>
+      </c>
+      <c r="K33" t="str">
+        <v>QR-MAT-ADIC-015</v>
+      </c>
+      <c r="L33" t="str">
+        <v>LOC-MAT-ADIC-015</v>
+      </c>
+      <c r="M33" t="str">
+        <v>TAG-MAT-ADIC-015</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N33"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N33"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C36"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="78.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Fila en Inventario</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Resultado esperado</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Caso de prueba</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Material válido con cantidad y varios identificadores.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>3</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Material válido sin cantidad ni identificador asignado.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>4</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Cantidad decimal con coma y unidad de medida.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>5</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Error intencional: falta el nombre o descripción del material.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>6</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Error intencional: cantidad negativa.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>7</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Error intencional: cantidad no numérica.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>8</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Error intencional: más de tres decimales.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Error intencional: cantidad supera el máximo de dígitos enteros.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>10</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Error intencional: código QR duplicado.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>11</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Error intencional: código interno duplicado.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>12</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Error intencional: observaciones de más de 2000 caracteres.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>13</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Error intencional: descripción de más de 1000 caracteres.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>14</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Error intencional: modelo de más de 255 caracteres.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Error intencional: CANTIDAD y CANTIDAD ACTUAL tienen valores contradictorios.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>16</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Error intencional: unidad de medida de más de 50 caracteres.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>17</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Fallida</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Error intencional: identificador ID de más de 255 caracteres.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>18</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Cantidad cero válida.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Registro válido adicional 001.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Registro válido adicional 002.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Registro válido adicional 003.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Registro válido adicional 004.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Registro válido adicional 005.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Registro válido adicional 006.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Registro válido adicional 007.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Registro válido adicional 008.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Registro válido adicional 009.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Registro válido adicional 010.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Registro válido adicional 011.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Registro válido adicional 012.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Registro válido adicional 013.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Registro válido adicional 014.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Exitosa</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Registro válido adicional 015.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Uso</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Carga únicamente la hoja Inventario; esta hoja documenta los resultados esperados.</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Nota</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Los casos fallidos son intencionales y sirven para verificar las validaciones del cargue.</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C36"/>
   </ignoredErrors>
 </worksheet>
 </file>